--- a/Trắc nghiệm bài kiểm tra đánh giá đầu vào/danhgianangluc/ba-frameworks-easy.xlsx
+++ b/Trắc nghiệm bài kiểm tra đánh giá đầu vào/danhgianangluc/ba-frameworks-easy.xlsx
@@ -460,19 +460,19 @@
         <v>SWOT là viết tắt của Strengths (Điểm mạnh), Weaknesses (Điểm yếu), Opportunities (Cơ hội), và Threats (Thách thức). Weaknesses là yếu tố nội bộ tiêu cực.</v>
       </c>
       <c r="F2" t="str">
-        <v>Weaknesses — Điểm yếu nội tại của doanh nghiệp hoặc sản phẩm cần khắc phục — yếu tố nội bộ tiêu cực</v>
+        <v>Websites — Hệ thống trang thông tin điện tử của doanh nghiệp — yếu tố kỹ thuật</v>
       </c>
       <c r="G2" t="str">
-        <v>Websites — Hệ thống trang thông tin điện tử của doanh nghiệp — yếu tố kỹ thuật</v>
+        <v>Wants — Những mong muốn chủ quan của ban giám đốc dự án — yếu tố mong muốn</v>
       </c>
       <c r="H2" t="str">
         <v>Workflows — Quy trình làm việc giữa các phòng ban trong công ty — quy trình vận hành</v>
       </c>
       <c r="I2" t="str">
-        <v>Wants — Những mong muốn chủ quan của ban giám đốc dự án — yếu tố mong muốn</v>
+        <v>Weaknesses — Điểm yếu nội tại của doanh nghiệp hoặc sản phẩm cần khắc phục — yếu tố nội bộ tiêu cực</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -492,19 +492,19 @@
         <v>PESTEL là công cụ phân tích các yếu tố vĩ mô bao gồm: Political (Chính trị), Economic (Kinh tế), Social (Xã hội), Technological (Công nghệ), Environmental (Môi trường), Legal (Pháp lý).</v>
       </c>
       <c r="F3" t="str">
-        <v>Các yếu tố vĩ mô ngoài tầm kiểm soát của doanh nghiệp ảnh hưởng đến môi trường kinh doanh — môi trường vĩ mô</v>
+        <v>Cấu trúc bảng và các mối quan hệ kho dữ liệu SQL của dự án — kỹ thuật database</v>
       </c>
       <c r="G3" t="str">
         <v>Năng suất làm việc hàng ngày của từng lập trình viên trong team — năng suất nội bộ</v>
       </c>
       <c r="H3" t="str">
-        <v>Cấu trúc bảng và các mối quan hệ kho dữ liệu SQL của dự án — kỹ thuật database</v>
+        <v>Các kịch bản kiểm thử bảo mật cho cổng thanh toán trực tuyến — bảo mật hệ thống</v>
       </c>
       <c r="I3" t="str">
-        <v>Các kịch bản kiểm thử bảo mật cho cổng thanh toán trực tuyến — bảo mật hệ thống</v>
+        <v>Các yếu tố vĩ mô ngoài tầm kiểm soát của doanh nghiệp ảnh hưởng đến môi trường kinh doanh — môi trường vĩ mô</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -524,19 +524,19 @@
         <v>Value Propositions (Tuyên bố giá trị) là lý do vì sao khách hàng chọn sản phẩm của bạn thay vì đối thủ. Nó giải quyết vấn đề hoặc đáp ứng nhu cầu cụ thể của khách hàng.</v>
       </c>
       <c r="F4" t="str">
+        <v>Tổng chi phí ước tính để duy trì hoạt động của máy chủ Cloud trong một năm — chi phí hạ tầng</v>
+      </c>
+      <c r="G4" t="str">
         <v>Tuyên bố giá trị độc đáo mà sản phẩm/dịch vụ mang lại để giải quyết nỗi đau của khách hàng — giá trị cốt lõi</v>
       </c>
-      <c r="G4" t="str">
+      <c r="H4" t="str">
+        <v>Các kênh truyền thông quảng cáo trực tuyến để tiếp cận người dùng — kênh tiếp thị</v>
+      </c>
+      <c r="I4" t="str">
         <v>Danh sách các đối thủ cạnh tranh trực tiếp trên thị trường — đối thủ cạnh tranh</v>
       </c>
-      <c r="H4" t="str">
-        <v>Tổng chi phí ước tính để duy trì hoạt động của máy chủ Cloud trong một năm — chi phí hạ tầng</v>
-      </c>
-      <c r="I4" t="str">
-        <v>Các kênh truyền thông quảng cáo trực tuyến để tiếp cận người dùng — kênh tiếp thị</v>
-      </c>
       <c r="J4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -556,7 +556,7 @@
         <v>Stakeholder (Bên liên quan) là mọi đối tượng có lợi ích, quyền lợi hoặc chịu tác động từ sự thành bại của dự án phần mềm.</v>
       </c>
       <c r="F5" t="str">
-        <v>Bất kỳ cá nhân hoặc tổ chức nào có ảnh hưởng hoặc chịu ảnh hưởng bởi quyết định/kết quả của dự án — bên liên quan</v>
+        <v>Những khách hàng đã mua sản phẩm và đánh giá 5 sao trên ứng dụng di động — khách hàng trung thành</v>
       </c>
       <c r="G5" t="str">
         <v>Chỉ duy nhất người đại diện ký hợp đồng thanh toán chi phí cho dự án — nhà tài trợ</v>
@@ -565,10 +565,10 @@
         <v>Lập trình viên chịu trách nhiệm viết tài liệu thiết kế hệ thống — kỹ sư hệ thống</v>
       </c>
       <c r="I5" t="str">
-        <v>Những khách hàng đã mua sản phẩm và đánh giá 5 sao trên ứng dụng di động — khách hàng trung thành</v>
+        <v>Bất kỳ cá nhân hoặc tổ chức nào có ảnh hưởng hoặc chịu ảnh hưởng bởi quyết định/kết quả của dự án — bên liên quan</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -588,19 +588,19 @@
         <v>BABOK là bộ tiêu chuẩn thế giới về phân tích nghiệp vụ, được nghiên cứu và phát triển bởi tổ chức phi lợi nhuận IIBA.</v>
       </c>
       <c r="F6" t="str">
+        <v>W3C (World Wide Web Consortium) — Tổ chức định chuẩn Web quốc tế</v>
+      </c>
+      <c r="G6" t="str">
         <v>IIBA (International Institute of Business Analysis) — Viện Phân tích Nghiệp vụ Quốc tế</v>
       </c>
-      <c r="G6" t="str">
+      <c r="H6" t="str">
         <v>PMI (Project Management Institute) — Viện Quản lý Dự án Hoa Kỳ</v>
       </c>
-      <c r="H6" t="str">
+      <c r="I6" t="str">
         <v>IEEE (Institute of Electrical and Electronics Engineers) — Viện Kỹ sư Điện và Điện tử</v>
       </c>
-      <c r="I6" t="str">
-        <v>W3C (World Wide Web Consortium) — Tổ chức định chuẩn Web quốc tế</v>
-      </c>
       <c r="J6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -620,19 +620,19 @@
         <v>RACI là viết tắt của: Responsible (Người thực hiện), Accountable (Người phê duyệt/Giải trình tối cao), Consulted (Người tham vấn), Informed (Người nhận thông tin). Chỉ có duy nhất 1 chữ "A" cho mỗi đầu việc.</v>
       </c>
       <c r="F7" t="str">
+        <v>Approved — Khách hàng đã ký biên bản nghiệm thu bàn giao sản phẩm — phê duyệt nghiệm thu</v>
+      </c>
+      <c r="G7" t="str">
         <v>Accountable — Người chịu trách nhiệm phê duyệt cuối cùng và sở hữu kết quả công việc — người chịu trách nhiệm tối cao</v>
       </c>
-      <c r="G7" t="str">
+      <c r="H7" t="str">
+        <v>Analyst — Business Analyst chịu trách nhiệm viết tài liệu mô tả yêu cầu — nhà phân tích</v>
+      </c>
+      <c r="I7" t="str">
         <v>Assigned — Lập trình viên được phân công trực tiếp vào code chức năng đó — người thực hiện</v>
       </c>
-      <c r="H7" t="str">
-        <v>Approved — Khách hàng đã ký biên bản nghiệm thu bàn giao sản phẩm — phê duyệt nghiệm thu</v>
-      </c>
-      <c r="I7" t="str">
-        <v>Analyst — Business Analyst chịu trách nhiệm viết tài liệu mô tả yêu cầu — nhà phân tích</v>
-      </c>
       <c r="J7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -652,19 +652,19 @@
         <v>Porter's Five Forces phân tích 5 áp lực: Đối thủ cạnh tranh ngành, Quyền lực nhà cung cấp, Quyền lực người mua, Đe dọa từ sản phẩm thay thế, và Đe dọa từ đối thủ mới.</v>
       </c>
       <c r="F8" t="str">
+        <v>Kế hoạch phân chia ca làm việc cho nhân sự trực tổng đài hỗ trợ khách hàng — phân ca làm việc</v>
+      </c>
+      <c r="G8" t="str">
         <v>Mức độ cạnh tranh và tính hấp dẫn về mặt lợi nhuận của một ngành công nghiệp — phân tích cấu trúc ngành</v>
-      </c>
-      <c r="G8" t="str">
-        <v>Số lượng lỗi tối đa mà hệ thống phần mềm có thể chấp nhận trước khi sập — giới hạn lỗi kỹ thuật</v>
       </c>
       <c r="H8" t="str">
         <v>Các công nghệ lập trình Frontend phổ biến nhất trong năm hiện tại — xu hướng kỹ thuật</v>
       </c>
       <c r="I8" t="str">
-        <v>Kế hoạch phân chia ca làm việc cho nhân sự trực tổng đài hỗ trợ khách hàng — phân ca làm việc</v>
+        <v>Số lượng lỗi tối đa mà hệ thống phần mềm có thể chấp nhận trước khi sập — giới hạn lỗi kỹ thuật</v>
       </c>
       <c r="J8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -684,19 +684,19 @@
         <v>Strengths và Weaknesses là các yếu tố nội bộ (Internal). Opportunities và Threats là các yếu tố thuộc môi trường bên ngoài (External).</v>
       </c>
       <c r="F9" t="str">
+        <v>Quy định về thời gian làm việc hành chính của nhân viên trong công ty — quy định hành chính</v>
+      </c>
+      <c r="G9" t="str">
         <v>Môi trường bên ngoài doanh nghiệp, doanh nghiệp không thể chủ động kiểm soát hoàn toàn — yếu tố ngoại cảnh</v>
       </c>
-      <c r="G9" t="str">
+      <c r="H9" t="str">
         <v>Nội tại bên trong doanh nghiệp, do ban giám đốc tự quyết định và điều chỉnh — yếu tố nội bộ</v>
       </c>
-      <c r="H9" t="str">
+      <c r="I9" t="str">
         <v>Đội ngũ phát triển phần mềm và các công cụ lập trình đang sử dụng — yếu tố kỹ thuật</v>
       </c>
-      <c r="I9" t="str">
-        <v>Quy định về thời gian làm việc hành chính của nhân viên trong công ty — quy định hành chính</v>
-      </c>
       <c r="J9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -719,13 +719,13 @@
         <v>Đặt câu hỏi "Tại sao" liên tiếp để tìm ra nguyên nhân gốc rễ (Root Cause) của một vấn đề nghiệp vụ — tìm nguyên nhân gốc rễ</v>
       </c>
       <c r="G10" t="str">
-        <v>Xây dựng 5 kịch bản kiểm thử tự động cho giao diện trang chủ của website — kiểm thử tự động</v>
+        <v>Phân chia dự án thành đúng 5 giai đoạn phát triển phần mềm tuần tự — phân chia giai đoạn</v>
       </c>
       <c r="H10" t="str">
         <v>Thuyết phục khách hàng ký hợp đồng dự án trong vòng 5 ngày làm việc — đàm phán hợp đồng</v>
       </c>
       <c r="I10" t="str">
-        <v>Phân chia dự án thành đúng 5 giai đoạn phát triển phần mềm tuần tự — phân chia giai đoạn</v>
+        <v>Xây dựng 5 kịch bản kiểm thử tự động cho giao diện trang chủ của website — kiểm thử tự động</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -748,19 +748,19 @@
         <v>Phân tích GAP yêu cầu BA làm rõ quy trình hiện tại (As-Is) và quy trình tương lai mong muốn (To-Be) để xác định khoảng trống (Gap) cần giải quyết bằng phần mềm.</v>
       </c>
       <c r="F11" t="str">
+        <v>As-Is: Dữ liệu mẫu ban đầu; To-Be: Báo cáo kết quả phân tích cuối cùng — trạng thái dữ liệu</v>
+      </c>
+      <c r="G11" t="str">
+        <v>As-Is: Lập trình viên thử việc; To-Be: Lập trình viên đã ký hợp đồng chính thức — trạng thái nhân sự</v>
+      </c>
+      <c r="H11" t="str">
         <v>As-Is: Quy trình hiện tại đang vận hành; To-Be: Quy trình cải tiến mong muốn sau khi áp dụng phần mềm — trạng thái quy trình</v>
       </c>
-      <c r="G11" t="str">
+      <c r="I11" t="str">
         <v>As-Is: Giao diện nháp vẽ tay; To-Be: Giao diện đã lập trình xong bằng code — trạng thái giao diện</v>
       </c>
-      <c r="H11" t="str">
-        <v>As-Is: Dữ liệu mẫu ban đầu; To-Be: Báo cáo kết quả phân tích cuối cùng — trạng thái dữ liệu</v>
-      </c>
-      <c r="I11" t="str">
-        <v>As-Is: Lập trình viên thử việc; To-Be: Lập trình viên đã ký hợp đồng chính thức — trạng thái nhân sự</v>
-      </c>
       <c r="J11">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
